--- a/data-tables/Datas/__tables__.xlsx
+++ b/data-tables/Datas/__tables__.xlsx
@@ -434,12 +434,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
@@ -575,12 +575,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>upgrades</t>
+          <t>activities</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>upgrades.xlsx</t>
+          <t>activities.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -598,12 +598,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>constants</t>
+          <t>activity_outputs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>constants.xlsx</t>
+          <t>activity_outputs.xlsx</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -621,12 +621,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>milestones</t>
+          <t>upgrades</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>milestones.xlsx</t>
+          <t>upgrades.xlsx</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -644,20 +644,66 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
+          <t>constants</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>constants.xlsx</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>milestones</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>milestones.xlsx</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>prestige_layers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>prestige_layers.xlsx</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>id</t>
         </is>
